--- a/数值知识库-网页版GPT/源表/Z-PayMent-支付表.xlsx
+++ b/数值知识库-网页版GPT/源表/Z-PayMent-支付表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\sldh-config\Config\Excels\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E87629-CC89-4E5B-B161-8EF9387FD60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F099A5B-526B-442D-9AB3-49049DC8340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,30 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>￥30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>￥648</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>￥6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>￥68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>￥198</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>￥328</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>$ 0.99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -327,6 +303,100 @@
   </si>
   <si>
     <t>$ 99.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProductId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品ID
+(关联到：游戏产品表
+原：game-product-tpl表)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.009</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.049</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.299</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.499</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.diamond.999</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.smallmonthcard.049</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.bigmonthcard.099</t>
+  </si>
+  <si>
+    <t>com.shoufang.sldh.firstrecharge.009</t>
+  </si>
+  <si>
+    <t>6元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>198元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>328元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>648元档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>49.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99.99刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30刀档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68刀档</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -809,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.875" customWidth="1"/>
@@ -820,11 +890,11 @@
     <col min="7" max="7" width="14.75" customWidth="1"/>
     <col min="8" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="9" style="12"/>
-    <col min="10" max="10" width="19.125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="30.5" customWidth="1"/>
+    <col min="10" max="11" width="19.125" style="13" customWidth="1"/>
+    <col min="12" max="13" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -852,22 +922,26 @@
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1"/>
+      <c r="L1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="1"/>
       <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:15" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -895,14 +969,17 @@
       <c r="J3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="L3" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
@@ -930,14 +1007,17 @@
       <c r="J4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="8" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>47</v>
       </c>
@@ -968,14 +1048,20 @@
       <c r="J5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -990,13 +1076,15 @@
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="16"/>
-      <c r="K6" s="9"/>
+      <c r="K6" s="16"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>100010001</v>
       </c>
@@ -1015,17 +1103,23 @@
       <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="12">
-        <v>6</v>
+      <c r="I7" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>100010002</v>
       </c>
@@ -1044,17 +1138,23 @@
       <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="12">
-        <v>30</v>
+      <c r="I8" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>100010003</v>
       </c>
@@ -1074,16 +1174,22 @@
         <v>32</v>
       </c>
       <c r="I9" s="12">
-        <v>68</v>
+        <v>9.99</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>100010004</v>
       </c>
@@ -1103,16 +1209,22 @@
         <v>33</v>
       </c>
       <c r="I10" s="12">
-        <v>198</v>
+        <v>29.99</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>100010005</v>
       </c>
@@ -1132,16 +1244,22 @@
         <v>34</v>
       </c>
       <c r="I11" s="12">
-        <v>328</v>
+        <v>49.99</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>100010006</v>
       </c>
@@ -1161,16 +1279,22 @@
         <v>35</v>
       </c>
       <c r="I12" s="12">
-        <v>648</v>
+        <v>99.99</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>100020001</v>
       </c>
@@ -1187,10 +1311,16 @@
         <v>30</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>100020002</v>
       </c>
@@ -1207,10 +1337,16 @@
         <v>68</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>100030001</v>
       </c>
@@ -1223,14 +1359,20 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="I15" s="12">
-        <v>6</v>
+      <c r="I15" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>21</v>
       </c>
@@ -1245,13 +1387,15 @@
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c r="J16" s="16"/>
-      <c r="K16" s="9"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>300010001</v>
       </c>
@@ -1274,13 +1418,19 @@
         <v>57</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" t="s">
+        <v>60</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>300010002</v>
       </c>
@@ -1303,13 +1453,19 @@
         <v>58</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="K18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>300010003</v>
       </c>
@@ -1332,13 +1488,19 @@
         <v>9.99</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K19" t="s">
+        <v>62</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>300010004</v>
       </c>
@@ -1361,13 +1523,19 @@
         <v>29.99</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>300010005</v>
       </c>
@@ -1390,13 +1558,19 @@
         <v>49.99</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" t="s">
+        <v>64</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>300010006</v>
       </c>
@@ -1419,13 +1593,19 @@
         <v>99.99</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K22" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>300020001</v>
       </c>
@@ -1442,10 +1622,16 @@
         <v>30</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>300020002</v>
       </c>
@@ -1462,10 +1648,16 @@
         <v>68</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="M24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>300030001</v>
       </c>
@@ -1482,7 +1674,13 @@
         <v>57</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="M25" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
